--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/05_同类资源配置对比明细.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/05_同类资源配置对比明细.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azs1\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-kk_29knp\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABFE1D3D-118B-4A6B-A7D6-73597AFEAEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A00C860-E2A8-4FE8-8ED0-5E46A4046BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-3645" yWindow="-13320" windowWidth="5970" windowHeight="10455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概览" sheetId="1" r:id="rId1"/>
@@ -898,7 +898,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D852-40B3-9AEC-AC21A3CEEFDB}"/>
+              <c16:uniqueId val="{00000000-02FD-475B-9C31-475ECAA731D8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/05_同类资源配置对比明细.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/05_同类资源配置对比明细.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-kk_29knp\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-lhcbnfs4\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A00C860-E2A8-4FE8-8ED0-5E46A4046BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329E3ADB-7EA1-44D4-A937-256700899CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3645" yWindow="-13320" windowWidth="5970" windowHeight="10455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17190" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概览" sheetId="1" r:id="rId1"/>
@@ -898,7 +898,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-02FD-475B-9C31-475ECAA731D8}"/>
+              <c16:uniqueId val="{00000000-472A-411A-87DF-B7B5A7DA1093}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/05_同类资源配置对比明细.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/05_同类资源配置对比明细.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-lhcbnfs4\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-yb_0tvu1\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329E3ADB-7EA1-44D4-A937-256700899CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17F2897-D317-47B8-9C29-037A1A796B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17190" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -898,7 +898,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-472A-411A-87DF-B7B5A7DA1093}"/>
+              <c16:uniqueId val="{00000000-0C0C-455F-B8C3-96ACD68CCF89}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/05_同类资源配置对比明细.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/05_同类资源配置对比明细.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-yb_0tvu1\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-09jfy2fk\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17F2897-D317-47B8-9C29-037A1A796B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82561CD-1865-4AFF-93B9-329A4E3913F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17190" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2660" yWindow="2660" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概览" sheetId="1" r:id="rId1"/>
@@ -898,7 +898,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0C0C-455F-B8C3-96ACD68CCF89}"/>
+              <c16:uniqueId val="{00000000-8017-4038-B56F-76ED79638D8C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/05_同类资源配置对比明细.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/05_同类资源配置对比明细.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-09jfy2fk\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-5yxkm8zf\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82561CD-1865-4AFF-93B9-329A4E3913F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6FF118D-5684-407B-BBD2-520D8D5E3B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2660" yWindow="2660" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概览" sheetId="1" r:id="rId1"/>
@@ -898,7 +898,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8017-4038-B56F-76ED79638D8C}"/>
+              <c16:uniqueId val="{00000000-09E3-4863-9087-C881FD71821A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/05_同类资源配置对比明细.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/05_同类资源配置对比明细.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-5yxkm8zf\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-do642wo4\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6FF118D-5684-407B-BBD2-520D8D5E3B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E853D1-4D00-4AE1-BF77-281D27CA7217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概览" sheetId="1" r:id="rId1"/>
@@ -898,7 +898,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-09E3-4863-9087-C881FD71821A}"/>
+              <c16:uniqueId val="{00000000-EB74-4947-8385-70A9B6207BA5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/05_同类资源配置对比明细.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/05_同类资源配置对比明细.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-do642wo4\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-jluf97rf\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E853D1-4D00-4AE1-BF77-281D27CA7217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7633A136-1005-4983-8659-7C0F78D646DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -898,7 +898,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-EB74-4947-8385-70A9B6207BA5}"/>
+              <c16:uniqueId val="{00000000-175A-447A-B6F0-B3A417D00A32}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/05_同类资源配置对比明细.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/05_同类资源配置对比明细.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-jluf97rf\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-4z_oecii\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7633A136-1005-4983-8659-7C0F78D646DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3458FCDB-7287-4BDB-8D37-BE48F234548A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概览" sheetId="1" r:id="rId1"/>
@@ -898,7 +898,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-175A-447A-B6F0-B3A417D00A32}"/>
+              <c16:uniqueId val="{00000000-91E8-4516-B6E8-168AE3C85483}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/05_同类资源配置对比明细.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/05_同类资源配置对比明细.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-4z_oecii\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-gq0eyj71\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3458FCDB-7287-4BDB-8D37-BE48F234548A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59D6AEDB-98B7-4E13-8514-691B84DF1C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2280" yWindow="2280" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -251,7 +251,7 @@
 1 条防火墙规则名称为门户按钮自动生成格式（ClientIPAddress_日期 / AllowAll_日期），说明是在门户里点“添加当前客户端 IP / 允许全部”加上的</t>
   </si>
   <si>
-    <t>R5-092698、S-N4-b385e1、O2-d2ae2f</t>
+    <t>R5-092698、R9-6d951f、S-N4-b385e1、O2-d2ae2f</t>
   </si>
   <si>
     <t>为服务器创建私有终结点（或复用已有终结点），把应用连接串切到私有地址后删除全部公网防火墙规则并关闭公网访问；把 require_secure_transport 改为 ON（动态参数，无需重启）；把高可用改为跨可用区（先关闭同可用区 HA 再按跨可用区重新开启，确认区域支持）；把备份保留期调到 14 天</t>
@@ -898,7 +898,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-91E8-4516-B6E8-168AE3C85483}"/>
+              <c16:uniqueId val="{00000000-A4B6-49E5-B009-EECA49D3D50D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/05_同类资源配置对比明细.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/05_同类资源配置对比明细.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-gq0eyj71\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-9n18lti6\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59D6AEDB-98B7-4E13-8514-691B84DF1C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB958A72-02EF-480E-BF35-B572E3C6DE62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2280" yWindow="2280" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -898,7 +898,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A4B6-49E5-B009-EECA49D3D50D}"/>
+              <c16:uniqueId val="{00000000-91F6-49BF-B367-6F15DB69E9F9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/05_同类资源配置对比明细.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/05_同类资源配置对比明细.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30625"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-9n18lti6\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-f6nzzhop\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB958A72-02EF-480E-BF35-B572E3C6DE62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4922F52F-9E63-42BF-8478-0DC6011116B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概览" sheetId="1" r:id="rId1"/>
@@ -898,7 +898,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-91F6-49BF-B367-6F15DB69E9F9}"/>
+              <c16:uniqueId val="{00000000-0F25-4D09-BC7D-C8377DF4DC43}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
